--- a/pensum/ok05/OK05_Kalkulasjon_Regneark_Timepris_og_kalkyle.xlsx
+++ b/pensum/ok05/OK05_Kalkulasjon_Regneark_Timepris_og_kalkyle.xlsx
@@ -1280,7 +1280,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1447,6 +1447,14 @@
     </xf>
     <xf numFmtId="168" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1781,7 +1789,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
@@ -2108,11 +2116,11 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="25" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c s="42" r="B25" t="s">
         <v>65</v>
       </c>
       <c r="C25" s="20" t="s">
@@ -2563,8 +2571,8 @@
         <v>137</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="22" t="s">
+    <row ht="27" customHeight="true" r="37" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="43" r="A37" t="s">
         <v>138</v>
       </c>
       <c r="B37" s="34" t="n">
@@ -3504,8 +3512,8 @@
         <v>247</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="20" t="s">
+    <row ht="27" customHeight="true" r="45" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A45" t="s">
         <v>248</v>
       </c>
       <c r="B45" s="30" t="n">
